--- a/DEAI/WEEK 11/Practicum 4/logs/experiment_results.xlsx
+++ b/DEAI/WEEK 11/Practicum 4/logs/experiment_results.xlsx
@@ -506,62 +506,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7708</v>
+        <v>15416</v>
       </c>
       <c r="D2" t="n">
-        <v>6166</v>
+        <v>26958</v>
       </c>
       <c r="E2" t="n">
-        <v>1542</v>
+        <v>3084</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(8,)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9365877392150502</v>
+        <v>0.915386898137844</v>
       </c>
       <c r="M2" t="n">
         <v>0.9377431906614786</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9076393347495767</v>
+        <v>0.9168326381966355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.908637123642526</v>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2348271427293944</v>
+        <v>0.2845835216559404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>0.5</v>
@@ -570,108 +570,108 @@
         <v>7708</v>
       </c>
       <c r="D3" t="n">
-        <v>6166</v>
+        <v>13476</v>
       </c>
       <c r="E3" t="n">
         <v>1542</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(16,)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K3" t="n">
         <v>0.0001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9367499189101525</v>
+        <v>0.9151825467497774</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.937094682230869</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9078487937908101</v>
+        <v>0.9164490074106245</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9085968616574723</v>
       </c>
       <c r="P3" t="n">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2272935598368508</v>
+        <v>0.2728648020334264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>7708</v>
+        <v>15416</v>
       </c>
       <c r="D4" t="n">
-        <v>6166</v>
+        <v>26958</v>
       </c>
       <c r="E4" t="n">
-        <v>1542</v>
+        <v>3084</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(32,)</t>
+          <t>(16,)</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>0.001</v>
       </c>
       <c r="J4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
         <v>0.0001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9364255595199481</v>
+        <v>0.9151643296980488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.937094682230869</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9074152667046543</v>
+        <v>0.9165971973800975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9079560727096823</v>
       </c>
       <c r="P4" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2323822370959314</v>
+        <v>0.2741448555996447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>0.5</v>
@@ -680,53 +680,53 @@
         <v>7708</v>
       </c>
       <c r="D5" t="n">
-        <v>6166</v>
+        <v>13476</v>
       </c>
       <c r="E5" t="n">
         <v>1542</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(16,)</t>
+          <t>(32,)</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
         <v>0.001</v>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
         <v>0.0001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9369120986052546</v>
+        <v>0.9131047788661324</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9364461738002594</v>
       </c>
       <c r="N5" t="n">
-        <v>0.908173469858171</v>
+        <v>0.9143858150081264</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9078531311700146</v>
       </c>
       <c r="P5" t="n">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2319235049935273</v>
+        <v>0.2579227926944561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -735,53 +735,53 @@
         <v>15416</v>
       </c>
       <c r="D6" t="n">
-        <v>12332</v>
+        <v>26958</v>
       </c>
       <c r="E6" t="n">
         <v>3084</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(16,)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.9159062244973663</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.935473411154345</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9154487996066648</v>
+        <v>0.9172808098812674</v>
       </c>
       <c r="O6" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9060269504480759</v>
       </c>
       <c r="P6" t="n">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.224631997713796</v>
+        <v>0.2663407218469365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -790,21 +790,21 @@
         <v>15416</v>
       </c>
       <c r="D7" t="n">
-        <v>12332</v>
+        <v>26958</v>
       </c>
       <c r="E7" t="n">
         <v>3084</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(32,)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I7" t="n">
         <v>0.001</v>
@@ -816,39 +816,39 @@
         <v>0.0001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9421829386960753</v>
+        <v>0.9159433192373322</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9351491569390402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.915572966340902</v>
+        <v>0.9172942155990743</v>
       </c>
       <c r="O7" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9054758221672209</v>
       </c>
       <c r="P7" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2211777323060725</v>
+        <v>0.2690901469316662</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="n">
-        <v>15416</v>
+        <v>7708</v>
       </c>
       <c r="D8" t="n">
-        <v>12332</v>
+        <v>13476</v>
       </c>
       <c r="E8" t="n">
-        <v>3084</v>
+        <v>1542</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -862,91 +862,91 @@
         <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="J8" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="K8" t="n">
         <v>0.0001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.9154051647373108</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.933852140077821</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9154487996066648</v>
+        <v>0.9166396005368075</v>
       </c>
       <c r="O8" t="n">
-        <v>0.908637123642526</v>
+        <v>0.904503817663203</v>
       </c>
       <c r="P8" t="n">
-        <v>92</v>
+        <v>300</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2249106403485807</v>
+        <v>0.2651592329135042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C9" t="n">
-        <v>15416</v>
+        <v>7708</v>
       </c>
       <c r="D9" t="n">
-        <v>12332</v>
+        <v>13476</v>
       </c>
       <c r="E9" t="n">
-        <v>3084</v>
+        <v>1542</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(32, 16)</t>
+          <t>(8,)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>0.001</v>
       </c>
       <c r="J9" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K9" t="n">
         <v>0.0001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9421829386960753</v>
+        <v>0.9132531908578213</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9332036316472114</v>
       </c>
       <c r="N9" t="n">
-        <v>0.915572966340902</v>
+        <v>0.9145768246156947</v>
       </c>
       <c r="O9" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9033248239728634</v>
       </c>
       <c r="P9" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2163886878763794</v>
+        <v>0.2858715234770828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -955,213 +955,213 @@
         <v>15416</v>
       </c>
       <c r="D10" t="n">
-        <v>12332</v>
+        <v>26958</v>
       </c>
       <c r="E10" t="n">
         <v>3084</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(32,)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J10" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K10" t="n">
         <v>0.0001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.914533719118629</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9335278858625162</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9154487996066648</v>
+        <v>0.9159236922583283</v>
       </c>
       <c r="O10" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9032399239867104</v>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2245692149045587</v>
+        <v>0.2711366346396156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C11" t="n">
-        <v>15416</v>
+        <v>7708</v>
       </c>
       <c r="D11" t="n">
-        <v>12332</v>
+        <v>13476</v>
       </c>
       <c r="E11" t="n">
-        <v>3084</v>
+        <v>1542</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(32, 16, 8)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
         <v>0.001</v>
       </c>
       <c r="J11" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K11" t="n">
         <v>0.0001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.9150341347580885</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9312581063553826</v>
       </c>
       <c r="N11" t="n">
-        <v>0.915467187074292</v>
+        <v>0.9162391889577349</v>
       </c>
       <c r="O11" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9008998690463429</v>
       </c>
       <c r="P11" t="n">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2159298131275433</v>
+        <v>0.2565119982396928</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>15416</v>
+        <v>3854</v>
       </c>
       <c r="D12" t="n">
-        <v>12332</v>
+        <v>6747</v>
       </c>
       <c r="E12" t="n">
-        <v>3084</v>
+        <v>771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(8,)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K12" t="n">
         <v>0.0001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9421829386960753</v>
+        <v>0.9036608863198459</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9286640726329443</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9155546209678405</v>
+        <v>0.9053737624471805</v>
       </c>
       <c r="O12" t="n">
-        <v>0.908637123642526</v>
+        <v>0.8990785872159389</v>
       </c>
       <c r="P12" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2206216400915514</v>
+        <v>0.3063368512354044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C13" t="n">
-        <v>7708</v>
+        <v>3854</v>
       </c>
       <c r="D13" t="n">
-        <v>6166</v>
+        <v>6747</v>
       </c>
       <c r="E13" t="n">
-        <v>1542</v>
+        <v>771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(32, 16, 8)</t>
+          <t>(16,)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
         <v>0.001</v>
       </c>
       <c r="J13" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K13" t="n">
         <v>0.0001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9378851767758677</v>
+        <v>0.9063287386986809</v>
       </c>
       <c r="M13" t="n">
-        <v>0.937094682230869</v>
+        <v>0.9273670557717251</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9093290735598233</v>
+        <v>0.9079664034573361</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9084549873021107</v>
+        <v>0.8975960470797246</v>
       </c>
       <c r="P13" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2133931599611334</v>
+        <v>0.2832920298742749</v>
       </c>
     </row>
     <row r="14">
@@ -1175,7 +1175,7 @@
         <v>7708</v>
       </c>
       <c r="D14" t="n">
-        <v>6166</v>
+        <v>13476</v>
       </c>
       <c r="E14" t="n">
         <v>1542</v>
@@ -1201,27 +1201,27 @@
         <v>0.0001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.937236457995459</v>
+        <v>0.9212674384090235</v>
       </c>
       <c r="M14" t="n">
-        <v>0.937094682230869</v>
+        <v>0.9267185473411155</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9084930716030161</v>
+        <v>0.9220589752285225</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9084549873021107</v>
+        <v>0.8953060859349752</v>
       </c>
       <c r="P14" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2166328733623354</v>
+        <v>0.2179332897366677</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -1230,175 +1230,175 @@
         <v>15416</v>
       </c>
       <c r="D15" t="n">
-        <v>12332</v>
+        <v>26958</v>
       </c>
       <c r="E15" t="n">
         <v>3084</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(8,)</t>
+          <t>(32, 16)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
         <v>0.001</v>
       </c>
       <c r="J15" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K15" t="n">
         <v>0.0001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.9178351509755917</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9374189364461738</v>
+        <v>0.9260700389105059</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9154487996066648</v>
+        <v>0.9189821904896754</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9081430553181319</v>
+        <v>0.8937492416874532</v>
       </c>
       <c r="P15" t="n">
-        <v>131</v>
+        <v>300</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2285401976382321</v>
+        <v>0.2357007286086871</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>7708</v>
+        <v>15416</v>
       </c>
       <c r="D16" t="n">
-        <v>6166</v>
+        <v>26958</v>
       </c>
       <c r="E16" t="n">
-        <v>1542</v>
+        <v>3084</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(8,)</t>
+          <t>(32, 16, 8)</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="I16" t="n">
         <v>0.001</v>
       </c>
       <c r="J16" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K16" t="n">
         <v>0.0001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9365877392150502</v>
+        <v>0.9213220565323837</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9364461738002594</v>
+        <v>0.9247730220492867</v>
       </c>
       <c r="N16" t="n">
-        <v>0.907710857557694</v>
+        <v>0.9223039214047773</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9074173612176373</v>
+        <v>0.8916781790772017</v>
       </c>
       <c r="P16" t="n">
-        <v>150</v>
+        <v>298</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2400170746670328</v>
+        <v>0.2208553284299258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C17" t="n">
-        <v>7708</v>
+        <v>3854</v>
       </c>
       <c r="D17" t="n">
-        <v>6166</v>
+        <v>6747</v>
       </c>
       <c r="E17" t="n">
-        <v>1542</v>
+        <v>771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(32,)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K17" t="n">
         <v>0.0001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9380473564709698</v>
+        <v>0.9066251667407736</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9357976653696498</v>
+        <v>0.9221789883268483</v>
       </c>
       <c r="N17" t="n">
-        <v>0.909534309337651</v>
+        <v>0.9081745708181254</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9063774037963913</v>
+        <v>0.8911699310973358</v>
       </c>
       <c r="P17" t="n">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2206836190817711</v>
+        <v>0.2612906989392162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3854</v>
+        <v>15416</v>
       </c>
       <c r="D18" t="n">
-        <v>3083</v>
+        <v>26958</v>
       </c>
       <c r="E18" t="n">
-        <v>771</v>
+        <v>3084</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1421,27 +1421,27 @@
         <v>0.0001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9406422315926046</v>
+        <v>0.9158320350174345</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9225032425421531</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9119687626004559</v>
+        <v>0.9169707710709032</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9042514978248288</v>
+        <v>0.8894560420982206</v>
       </c>
       <c r="P18" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2101094016060385</v>
+        <v>0.2592791564874105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
         <v>0.25</v>
@@ -1450,7 +1450,7 @@
         <v>3854</v>
       </c>
       <c r="D19" t="n">
-        <v>3083</v>
+        <v>6747</v>
       </c>
       <c r="E19" t="n">
         <v>771</v>
@@ -1467,36 +1467,36 @@
         <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="J19" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="K19" t="n">
         <v>0.0001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9390204346415829</v>
+        <v>0.9064769527197273</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9195849546044098</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9099277409216514</v>
+        <v>0.9080684888515651</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9042514978248288</v>
+        <v>0.8874648958595275</v>
       </c>
       <c r="P19" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.225160282713124</v>
+        <v>0.2690412702685819</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
         <v>0.25</v>
@@ -1505,21 +1505,21 @@
         <v>3854</v>
       </c>
       <c r="D20" t="n">
-        <v>3083</v>
+        <v>6747</v>
       </c>
       <c r="E20" t="n">
         <v>771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(32,)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I20" t="n">
         <v>0.001</v>
@@ -1531,27 +1531,27 @@
         <v>0.0001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9390204346415829</v>
+        <v>0.9183340744034386</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9169909208819714</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9099277409216514</v>
+        <v>0.9194001716686984</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9042514978248288</v>
+        <v>0.8846783946177089</v>
       </c>
       <c r="P20" t="n">
         <v>250</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2268294426883369</v>
+        <v>0.2563645513125783</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
         <v>0.25</v>
@@ -1560,24 +1560,24 @@
         <v>3854</v>
       </c>
       <c r="D21" t="n">
-        <v>3083</v>
+        <v>6747</v>
       </c>
       <c r="E21" t="n">
         <v>771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(32, 16)</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J21" t="n">
         <v>300</v>
@@ -1586,27 +1586,27 @@
         <v>0.0001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9390204346415829</v>
+        <v>0.9336001185712168</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9079118028534371</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9099277409216514</v>
+        <v>0.9340723426732335</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9042514978248288</v>
+        <v>0.8730315481571385</v>
       </c>
       <c r="P21" t="n">
         <v>300</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2306852997824585</v>
+        <v>0.1874424088079875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
         <v>0.25</v>
@@ -1615,131 +1615,131 @@
         <v>3854</v>
       </c>
       <c r="D22" t="n">
-        <v>3083</v>
+        <v>6747</v>
       </c>
       <c r="E22" t="n">
         <v>771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(16,)</t>
+          <t>(32, 16, 8)</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="I22" t="n">
         <v>0.001</v>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K22" t="n">
         <v>0.0001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9386960752513785</v>
+        <v>0.950348302949459</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9014267185473411</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9094834314838881</v>
+        <v>0.9503274537611119</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9042514978248288</v>
+        <v>0.8645849510607498</v>
       </c>
       <c r="P22" t="n">
-        <v>172</v>
+        <v>300</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2316422351398923</v>
+        <v>0.1522247252122676</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B23" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C23" t="n">
-        <v>3854</v>
+        <v>7708</v>
       </c>
       <c r="D23" t="n">
-        <v>3083</v>
+        <v>13476</v>
       </c>
       <c r="E23" t="n">
-        <v>771</v>
+        <v>1542</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(8,)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="J23" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K23" t="n">
         <v>0.0001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9386960752513785</v>
+        <v>0.9226031463342238</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9325551232166018</v>
+        <v>0.9007782101167315</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9094834314838881</v>
+        <v>0.9228368725525388</v>
       </c>
       <c r="O23" t="n">
-        <v>0.904051133077278</v>
+        <v>0.8642522435342781</v>
       </c>
       <c r="P23" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2468592638299372</v>
+        <v>0.2194431287839806</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C24" t="n">
-        <v>3854</v>
+        <v>7708</v>
       </c>
       <c r="D24" t="n">
-        <v>3083</v>
+        <v>13476</v>
       </c>
       <c r="E24" t="n">
-        <v>771</v>
+        <v>1542</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(32, 16)</t>
+          <t>(32, 16, 8)</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I24" t="n">
         <v>0.001</v>
@@ -1751,27 +1751,27 @@
         <v>0.0001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9396691534219915</v>
+        <v>0.9405609973285841</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9312581063553826</v>
+        <v>0.8994811932555123</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9106866277851373</v>
+        <v>0.9407097477040205</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9019483348895113</v>
+        <v>0.8610974258749559</v>
       </c>
       <c r="P24" t="n">
         <v>300</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.197782635292455</v>
+        <v>0.1733438217911961</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B25" t="n">
         <v>0.25</v>
@@ -1780,48 +1780,48 @@
         <v>3854</v>
       </c>
       <c r="D25" t="n">
-        <v>3083</v>
+        <v>6747</v>
       </c>
       <c r="E25" t="n">
         <v>771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(32, 16, 8)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="J25" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K25" t="n">
         <v>0.0001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9432371067142393</v>
+        <v>0.9297465540240106</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9286640726329443</v>
+        <v>0.8923476005188068</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9151430191464037</v>
+        <v>0.9301788056349064</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8976452109242142</v>
+        <v>0.8537562645985792</v>
       </c>
       <c r="P25" t="n">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1858806837182946</v>
+        <v>0.1952675255498859</v>
       </c>
     </row>
   </sheetData>
@@ -1927,62 +1927,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7708</v>
+        <v>15416</v>
       </c>
       <c r="D2" t="n">
-        <v>6166</v>
+        <v>26958</v>
       </c>
       <c r="E2" t="n">
-        <v>1542</v>
+        <v>3084</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(8,)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J2" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9365877392150502</v>
+        <v>0.915386898137844</v>
       </c>
       <c r="M2" t="n">
         <v>0.9377431906614786</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9076393347495767</v>
+        <v>0.9168326381966355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.908637123642526</v>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2348271427293944</v>
+        <v>0.2845835216559404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>0.5</v>
@@ -1991,108 +1991,108 @@
         <v>7708</v>
       </c>
       <c r="D3" t="n">
-        <v>6166</v>
+        <v>13476</v>
       </c>
       <c r="E3" t="n">
         <v>1542</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(16, 8)</t>
+          <t>(16,)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K3" t="n">
         <v>0.0001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9367499189101525</v>
+        <v>0.9151825467497774</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.937094682230869</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9078487937908101</v>
+        <v>0.9164490074106245</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9085968616574723</v>
       </c>
       <c r="P3" t="n">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2272935598368508</v>
+        <v>0.2728648020334264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>7708</v>
+        <v>15416</v>
       </c>
       <c r="D4" t="n">
-        <v>6166</v>
+        <v>26958</v>
       </c>
       <c r="E4" t="n">
-        <v>1542</v>
+        <v>3084</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(32,)</t>
+          <t>(16,)</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>0.001</v>
       </c>
       <c r="J4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
         <v>0.0001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9364255595199481</v>
+        <v>0.9151643296980488</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.937094682230869</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9074152667046543</v>
+        <v>0.9165971973800975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9079560727096823</v>
       </c>
       <c r="P4" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2323822370959314</v>
+        <v>0.2741448555996447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>0.5</v>
@@ -2101,53 +2101,53 @@
         <v>7708</v>
       </c>
       <c r="D5" t="n">
-        <v>6166</v>
+        <v>13476</v>
       </c>
       <c r="E5" t="n">
         <v>1542</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(16,)</t>
+          <t>(32,)</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
         <v>0.001</v>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
         <v>0.0001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9369120986052546</v>
+        <v>0.9131047788661324</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.9364461738002594</v>
       </c>
       <c r="N5" t="n">
-        <v>0.908173469858171</v>
+        <v>0.9143858150081264</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9094874040314761</v>
+        <v>0.9078531311700146</v>
       </c>
       <c r="P5" t="n">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2319235049935273</v>
+        <v>0.2579227926944561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -2156,48 +2156,48 @@
         <v>15416</v>
       </c>
       <c r="D6" t="n">
-        <v>12332</v>
+        <v>26958</v>
       </c>
       <c r="E6" t="n">
         <v>3084</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(16,)</t>
+          <t>(16, 8)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K6" t="n">
         <v>0.0001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9421018488485242</v>
+        <v>0.9159062244973663</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9377431906614786</v>
+        <v>0.935473411154345</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9154487996066648</v>
+        <v>0.9172808098812674</v>
       </c>
       <c r="O6" t="n">
-        <v>0.908637123642526</v>
+        <v>0.9060269504480759</v>
       </c>
       <c r="P6" t="n">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.224631997713796</v>
+        <v>0.2663407218469365</v>
       </c>
     </row>
   </sheetData>
